--- a/exports/AsistDoc_Redes_II_Notas.xlsx
+++ b/exports/AsistDoc_Redes_II_Notas.xlsx
@@ -492,7 +492,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Periodo Lectivo: 2026-II | Fecha de Generación: 20/10/2026 02:46</t>
+          <t>Periodo Lectivo: 2026-II | Fecha de Generación: 20/10/2026 03:22</t>
         </is>
       </c>
     </row>

--- a/exports/AsistDoc_Redes_II_Notas.xlsx
+++ b/exports/AsistDoc_Redes_II_Notas.xlsx
@@ -492,7 +492,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Periodo Lectivo: 2026-II | Fecha de Generación: 20/10/2026 03:22</t>
+          <t>Periodo Lectivo: 2026-II | Fecha de Generación: 20/10/2026 03:56</t>
         </is>
       </c>
     </row>

--- a/exports/AsistDoc_Redes_II_Notas.xlsx
+++ b/exports/AsistDoc_Redes_II_Notas.xlsx
@@ -492,7 +492,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Periodo Lectivo: 2026-II | Fecha de Generación: 20/10/2026 03:56</t>
+          <t>Periodo Lectivo: 2026-II | Fecha de Generación: 24/10/2026 14:16</t>
         </is>
       </c>
     </row>

--- a/exports/AsistDoc_Redes_II_Notas.xlsx
+++ b/exports/AsistDoc_Redes_II_Notas.xlsx
@@ -492,7 +492,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Periodo Lectivo: 2026-II | Fecha de Generación: 20/10/2026 03:56</t>
+          <t>Periodo Lectivo: 2026-II | Fecha de Generación: 25/10/2026 14:27</t>
         </is>
       </c>
     </row>

--- a/exports/AsistDoc_Redes_II_Notas.xlsx
+++ b/exports/AsistDoc_Redes_II_Notas.xlsx
@@ -492,7 +492,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Periodo Lectivo: 2026-II | Fecha de Generación: 20/10/2026 03:56</t>
+          <t>Periodo Lectivo: 2026-II | Fecha de Generación: 27/10/2026 14:10</t>
         </is>
       </c>
     </row>
